--- a/output/full_scan/batch_seq0_2026-07-01.xlsx
+++ b/output/full_scan/batch_seq0_2026-07-01.xlsx
@@ -428,23 +428,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
     <col width="7" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
@@ -527,54 +527,3446 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
+        <v>8176</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>智捷</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1110.795841372373</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>70.54361817964994</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>9.867309048437724</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>4.738747949130946</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.0550062069957536</v>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, williams_r_recovery, cci_momentum, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>8109</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>博大</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>995.157070611222</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>56.85315217516115</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>23.12910964340192</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0.6532671601544934</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.1563531371115276</v>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>8121</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>越峰</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>947.1252148360932</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>62.10936363872014</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>37.59485030663</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>2.040730979033626</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>-0.3562786393707133</v>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>8150</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>南茂</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>931.0159910994043</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>57.59411916071389</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>26.81978359952185</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>2.035029871580903</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>-0.508436193299961</v>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>8438</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>昶昕</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>842.381355004793</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>63.59935926457361</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>25.10476313360677</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>1.156658474144927</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>1.375623104582459</v>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>8071</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>能率網通</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>829.6325099321026</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>66.24768442635988</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>44.98068579461272</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>1.249857366764348</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0.1793220497989787</v>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>8069</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>元太</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>783.3115141684409</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>50.92265608078296</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>20.09127447257424</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>1.57356093001077</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0.09809787905406631</v>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8261</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>富鼎</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>768.6074572642929</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>297.5</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>77.709735642033</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>47.48992208653205</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>1.053917253376066</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>7.322422516231143</v>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>8091</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>翔名</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>762.6515947598018</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>275.5</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>58.52056329923722</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>30.54480181612509</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>1.101008100560503</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>-0.5328710407481925</v>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>8182</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>加高</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>743.6879254408886</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>59.67567240696605</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>24.89534049992437</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>1.427030495875765</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>-0.3463314492683969</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>8163</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>達方</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>727.1733944203801</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>52.76853729043128</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>37.45987507177093</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.5921283146979176</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>-0.7533487465269397</v>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>8112</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>至上</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>701.2401714124538</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>45.32343516026691</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>22.12560350705906</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0.589693068818998</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>-1.035899589789694</v>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>8227</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>巨有科技</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>689.1055748774312</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>198.5</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>52.43616963106035</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>16.92493187171427</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>1.641586487159422</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>1.822650573254194</v>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>9912</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>偉聯</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>674</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>47.01410793576691</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>31.67430755265539</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>7.752358427655621</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>-0.0155311762432739</v>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>8081</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>致新</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>610.8303563927043</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>309</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>55.91662648463198</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>26.43828076857665</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>1.456541483679003</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>0.1058516159483105</v>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
         <v>8996</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D2" s="2" t="n">
+      <c r="C17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D17" s="2" t="n">
         <v>600.5330602724589</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E17" s="2" t="n">
         <v>1555</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2" t="n">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="n">
         <v>63.9909333818806</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I17" s="2" t="n">
         <v>23.65647739318278</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J17" s="2" t="n">
         <v>0.2183950199595346</v>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N2" s="2" t="n">
+      <c r="K17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N17" s="2" t="n">
         <v>11.54318631018933</v>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>8093</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>保銳</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>595.4770451543096</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>54.12323041851817</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>8.621656361627425</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>0.6818939541671647</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>0.2638735616528413</v>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>8105</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>凌巨</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>591.0169497811215</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>21.65</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>53.60222503326603</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>40.80834213660821</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0.5806957463653735</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>-0.1979623809861741</v>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>8054</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>安國</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>587.7752536229385</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>56.4447474854156</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>24.14426572500701</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0.7761839384361525</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>1.270097713854323</v>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>8215</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>明基材</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>578.645088663881</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>49.09041104136544</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>23.92634764054577</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0.4006646869277015</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>-0.207647051023338</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>8070</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>長華*</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>560.670902559927</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>46.76671936254859</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>22.53365190872695</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>0.2913434859648606</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>-0.8773341701918669</v>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>8147</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>正淩</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>553.4478054620835</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>46.53133680102194</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>21.34246387741439</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>1.059137028705434</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>0.2906594861168976</v>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>8050</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>廣積</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>547.6493392319791</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>44.05241971908021</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>28.57523743400916</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0.4080072982898173</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>-0.9118139157755112</v>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>8049</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>晶采</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>523.1724974149606</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>50.17795571554093</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>27.16001369299875</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0.3572702589200145</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>-0.0511553367299006</v>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>8064</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>東捷</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>521.4779975722799</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>53.4917363483116</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>27.25936718831002</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>1.04101525642914</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>-2.37086240201322</v>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>8476</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>台境*</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>517.2083378142471</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>90.44881082790404</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>63.02425696907693</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0.7449097332396131</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>0.4350301317883673</v>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>8473</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>山林水</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>513.3587130166557</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>50.54018799760441</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>25.57506613924848</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0.4942138543486997</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>-0.7842429543992315</v>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>8131</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>福懋科</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>508.5179803798932</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>46.72888094859509</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>13.20649091082138</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0.8865415063730595</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>-0.7441324803875911</v>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>8088</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>品安</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>507.1934068928559</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>46.30633554271227</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>24.08638149430238</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0.4167086992933254</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>-0.6869719513150039</v>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>8162</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>微矽電子-創</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>486.9858313270825</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>54.93486038993835</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>40.10332382233811</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0.3928621190998826</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>-0.5160864400427769</v>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>8072</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>陞泰</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>484.9900412921818</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>50.80939564303962</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>23.91713682225708</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0.2777121715453796</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>-0.0792589611526068</v>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>8183</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>精星</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>465.7267858769903</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>58.10962152130483</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>19.31221677021287</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>0.8726785876990272</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>0.2713294803209648</v>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>8499</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>鼎炫-KY</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>431.6884956190485</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>300.5</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>50.59165614979263</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>16.96916761172215</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0.5168720431073091</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>0.1424625297687605</v>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>8104</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>錸寶</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>429.1320238521964</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>37.55</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>45.3745309030702</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>22.11725438149919</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0.2374495232272931</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>-0.5778693488634153</v>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>8110</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>華東</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>422.0743227285797</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>46.41241265921887</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>19.22786579491468</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0.5537386865273047</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>-0.5774622119436457</v>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>8155</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>博智</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>417.7985833472181</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>376</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>46.7781990910088</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>16.5220164000781</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>0.652600169086814</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>-1.371029786978364</v>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>8103</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>瀚荃</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>413.7362470833053</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>49.31767449616522</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>16.80353327697779</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>1.158309659921438</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>0.4651055598165787</v>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>8097</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>常珵</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>378.2007823967302</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>51.4284735146365</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>21.605102938854</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>0.6153494657721399</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>-0.2365278469392713</v>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>8111</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>立碁</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>376.7341796037434</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>35.27115426764431</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>27.35290037877445</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>0.7644387771019303</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>-0.1926360489688767</v>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>8210</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>369.4448106251783</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>1295</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>46.4556794163742</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>16.15747970021336</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>0.5911090452512445</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>-19.03305527176915</v>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>8086</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>宏捷科</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>359.2792827862272</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>42.55913757920098</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>16.48619092801401</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>0.8962154069116324</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>-1.895771310021184</v>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>8074</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>鉅橡</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>356.2862853567541</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>42.39584730798288</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>10.91771907089492</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>0.5988896540820132</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>-0.5281071509748285</v>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>8422</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>可寧衛*</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>354.8212311485042</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>41.56850278859179</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>13.59235475750666</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>1.146786635273807</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>-0.1665211915288389</v>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>8341</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>日友</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>352.6269236059839</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>37.06386346771427</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>23.18325532620882</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>0.5027824880802828</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>-0.6100194880274257</v>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>8076</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>伍豐</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>350.5627339967783</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>46.44865361847464</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>15.49411229519926</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>0.2406520255416949</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>-0.2778904313115847</v>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>8080</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>永利聯合</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>339.523810379097</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>46.21683781788526</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>47.06382694423503</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>0.9042119261543964</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>-0.0242976062140366</v>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>8084</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>巨虹</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>330.1960998704898</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>54.83645756675395</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>18.40280980961612</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>0.6454158231159436</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>-0.0238060670619185</v>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>9930</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>中聯資源</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>307.4082506657213</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>28.87330563632138</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>25.6605003448418</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>0.8764236365519245</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>-0.3875858699048083</v>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>8114</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>振樺電</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>305.4398257184493</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>32.77432210427223</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>22.29598801594764</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>0.3869294912426474</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>-3.867924671834397</v>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>8067</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>志旭</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>295.6999072640733</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>50.11433908531635</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>7.577162018028474</v>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>0.3688189086095483</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>-0.044128512717134</v>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>8171</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>天宇</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>292.5976652087361</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>42.7074775923293</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>20.07132282105488</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>0.4048759132037087</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>-0.0529627007724519</v>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>8068</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>全達</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>288.5260106108825</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>42.35607144299471</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>19.47736713088327</v>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>0.3440038851893618</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>0.0518925957089374</v>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>8102</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>傑霖科技</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>286.1492569045874</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>44.27328040351166</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>13.50432631142409</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>0.4406289101355378</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>-0.8022831391380386</v>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>8271</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>宇瞻</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>285.0453591685217</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>32.21442601997651</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>17.88048329588452</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>0.9106054154240646</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>-2.780895441445998</v>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>8087</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>華鎂鑫</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>231.4311860948568</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>41.80470273629104</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>13.58458957986164</v>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>0.4018747915435433</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>-0.2005365736215294</v>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>8213</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>志超</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>216.0334298860771</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>43.32844532357146</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>11.67383571489494</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>0.8620109332547338</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>-0.0550180585836583</v>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>8048</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>德勝</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>214.5134107222776</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>46.03532461612307</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>15.5318009790341</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>0.5403767124555975</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>-0.4204629059035292</v>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>8089</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>康全電訊</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>208.2175602373984</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>44.2806512085058</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>30.16414577037403</v>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>0.2722889595914037</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>-0.1008448812710504</v>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>9955</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>佳龍</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>195.0862186297984</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>38.49520989780745</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>23.91787006318023</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>0.5229525061375463</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>-0.002895489956487</v>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>8101</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>華冠</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>184.0778088356639</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>39.07654195581286</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>14.0304945137058</v>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>0.3142879888683901</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>-0.2943294678616175</v>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>8092</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>建暐</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>177.7200858232768</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>26.55092099782304</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>20.4428480961836</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>0.5720196620971356</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>-0.1324762751606956</v>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>8059</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>凱碩</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>161.9181228722707</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>32.29586495416856</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>21.52830595468004</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>0.873085877094844</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>-0.09861845521334579</v>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>無敵</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>150.6685888274262</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>44.95474553310149</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>17.87571441789742</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>0.37150009046731</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>-0.0707924052409805</v>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>8249</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>菱光</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>148.4472372604689</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>48.05</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>40.74369144864785</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>17.61163914908903</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>1.005440631198076</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>-0.5563345873294627</v>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>8085</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>福華</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>74.15288557183288</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>42.4280193213454</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>18.0145741041381</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>0.2565887218093056</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>-0.1221104786347467</v>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>

--- a/output/full_scan/batch_seq0_2026-07-01.xlsx
+++ b/output/full_scan/batch_seq0_2026-07-01.xlsx
@@ -428,11 +428,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O66"/>
+  <dimension ref="A1:O117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>70.54361817964994</v>
+        <v>70.54361794379261</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>9.867309048437724</v>
+        <v>9.867309097091669</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>4.738747949130946</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.0550062069957536</v>
+        <v>0.0550062071006905</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>56.85315217516115</v>
+        <v>56.85315218103685</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>23.12910964340192</v>
+        <v>23.12910972791241</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>0.6532671601544934</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1563531371115276</v>
+        <v>0.1563531370924539</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -633,21 +633,21 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8121</v>
+        <v>8442</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>947.1252148360932</v>
+        <v>955.1047867114356</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>50.8</v>
+        <v>42.2</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>62.10936363872014</v>
+        <v>54.22690148852296</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>37.59485030663</v>
+        <v>22.48092861435212</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2.040730979033626</v>
+        <v>2.42195526506846</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.3562786393707133</v>
+        <v>0.42880576971154</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>8150</v>
+        <v>8121</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>931.0159910994043</v>
+        <v>947.1252148360932</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>107</v>
+        <v>50.8</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>57.59411916071389</v>
+        <v>62.1093635712317</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>26.81978359952185</v>
+        <v>37.59485031438891</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.035029871580903</v>
+        <v>2.040730979033626</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.508436193299961</v>
+        <v>-0.3562786390177486</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>8438</v>
+        <v>8150</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>842.381355004793</v>
+        <v>931.0159910994043</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>101.5</v>
+        <v>107</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,49 +764,49 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>63.59935926457361</v>
+        <v>57.59411916220308</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>25.10476313360677</v>
+        <v>26.8197835098006</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.156658474144927</v>
+        <v>2.035029871580903</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1.375623104582459</v>
+        <v>-0.508436193299961</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>8071</v>
+        <v>8466</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>829.6325099321026</v>
+        <v>924.2528146420289</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>31.1</v>
+        <v>17.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>66.24768442635988</v>
+        <v>68.69399285335656</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>44.98068579461272</v>
+        <v>18.5726627254298</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.249857366764348</v>
+        <v>6.713192474979108</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1793220497989787</v>
+        <v>0.1476017783340432</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>8069</v>
+        <v>8438</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>783.3115141684409</v>
+        <v>842.381355004793</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>204</v>
+        <v>101.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,49 +870,49 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>50.92265608078296</v>
+        <v>63.59935927485985</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>20.09127447257424</v>
+        <v>25.10476312923759</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.57356093001077</v>
+        <v>1.156658474144927</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.09809787905406631</v>
+        <v>1.375623104572926</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8261</v>
+        <v>8071</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>768.6074572642929</v>
+        <v>829.6325099321026</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>297.5</v>
+        <v>31.1</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>77.709735642033</v>
+        <v>66.24768442899335</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>47.48992208653205</v>
+        <v>44.98068582490084</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.053917253376066</v>
+        <v>1.249857366764348</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>7.322422516231143</v>
+        <v>0.1793220498466778</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8091</v>
+        <v>8069</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>762.6515947598018</v>
+        <v>783.3115141684409</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>275.5</v>
+        <v>204</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,49 +976,49 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>58.52056329923722</v>
+        <v>50.92265601479062</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>30.54480181612509</v>
+        <v>20.09127443688138</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.101008100560503</v>
+        <v>1.57356093001077</v>
       </c>
       <c r="K10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.5328710407481925</v>
+        <v>0.09809787762308241</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8182</v>
+        <v>8261</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>743.6879254408886</v>
+        <v>768.6074572642929</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>54</v>
+        <v>297.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>59.67567240696605</v>
+        <v>77.7097356404569</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>24.89534049992437</v>
+        <v>47.48992200175938</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.427030495875765</v>
+        <v>1.053917253376066</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.3463314492683969</v>
+        <v>7.322422516479186</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8163</v>
+        <v>8222</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>727.1733944203801</v>
+        <v>764</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>41.3</v>
+        <v>40.75</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>52.76853729043128</v>
+        <v>66.59752931399112</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>37.45987507177093</v>
+        <v>16.56500373947244</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.5921283146979176</v>
+        <v>8.104591093780481</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.7533487465269397</v>
+        <v>0.5041342693676162</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8112</v>
+        <v>8091</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>701.2401714124538</v>
+        <v>762.6515947598018</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>89.7</v>
+        <v>275.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>45.32343516026691</v>
+        <v>58.52056326330044</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>22.12560350705906</v>
+        <v>30.544801853073</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.589693068818998</v>
+        <v>1.101008100560503</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-1.035899589789694</v>
+        <v>-0.532871039985011</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8227</v>
+        <v>8182</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>689.1055748774312</v>
+        <v>743.6879254408886</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>198.5</v>
+        <v>54</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,49 +1188,49 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>52.43616963106035</v>
+        <v>59.67567239927833</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>16.92493187171427</v>
+        <v>24.89534046178797</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.641586487159422</v>
+        <v>1.427030495875765</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>1.822650573254194</v>
+        <v>-0.3463314492493152</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>9912</v>
+        <v>8163</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>674</v>
+        <v>727.1733944203801</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>12.45</v>
+        <v>41.3</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>47.01410793576691</v>
+        <v>52.76853726371053</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>31.67430755265539</v>
+        <v>37.45987502534022</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>7.752358427655621</v>
+        <v>0.5921283146979176</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.0155311762432739</v>
+        <v>-0.7533487463552229</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8081</v>
+        <v>8926</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>610.8303563927043</v>
+        <v>715.1650555401129</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>309</v>
+        <v>74.3</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,49 +1294,49 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>55.91662648463198</v>
+        <v>54.15085909884382</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>26.43828076857665</v>
+        <v>46.51150333458023</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.456541483679003</v>
+        <v>0.7744404380027515</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.1058516159483105</v>
+        <v>-1.069668804336111</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8996</v>
+        <v>8464</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>600.5330602724589</v>
+        <v>710.1644040086514</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1555</v>
+        <v>357</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>63.9909333818806</v>
+        <v>60.21726709691307</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>23.65647739318278</v>
+        <v>16.49365516972886</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.2183950199595346</v>
+        <v>0.8149439904055238</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>11.54318631018933</v>
+        <v>0.955278600837886</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8093</v>
+        <v>8112</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>595.4770451543096</v>
+        <v>701.2401714124538</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>19.95</v>
+        <v>89.7</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,49 +1400,49 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>54.12323041851817</v>
+        <v>45.32343515269501</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>8.621656361627425</v>
+        <v>22.12560355564608</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.6818939541671647</v>
+        <v>0.589693068818998</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.2638735616528413</v>
+        <v>-1.035899589675218</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8105</v>
+        <v>8227</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>591.0169497811215</v>
+        <v>689.1055748774312</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>21.65</v>
+        <v>198.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,49 +1453,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>53.60222503326603</v>
+        <v>52.43616958658857</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>40.80834213660821</v>
+        <v>16.92493187271426</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.5806957463653735</v>
+        <v>1.641586487159422</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.1979623809861741</v>
+        <v>1.822650574494361</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8054</v>
+        <v>9912</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>587.7752536229385</v>
+        <v>674</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>118.5</v>
+        <v>12.45</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>56.4447474854156</v>
+        <v>47.01410785803681</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>24.14426572500701</v>
+        <v>31.67430742941625</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.7761839384361525</v>
+        <v>7.752358427655621</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.270097713854323</v>
+        <v>-0.0155311762241929</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8215</v>
+        <v>8289</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>578.645088663881</v>
+        <v>629.2854665158306</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>29.15</v>
+        <v>61.7</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>49.09041104136544</v>
+        <v>48.32231620351827</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>23.92634764054577</v>
+        <v>22.20600291841189</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.4006646869277015</v>
+        <v>1.352689503322028</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.207647051023338</v>
+        <v>-1.45467435772824</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8070</v>
+        <v>8081</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>560.670902559927</v>
+        <v>610.8303563927043</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>53.4</v>
+        <v>309</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,49 +1612,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>46.76671936254859</v>
+        <v>55.91662649648929</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>22.53365190872695</v>
+        <v>26.43828071641095</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.2913434859648606</v>
+        <v>1.456541483679003</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.8773341701918669</v>
+        <v>0.1058516164252925</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8147</v>
+        <v>8996</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>553.4478054620835</v>
+        <v>600.5330602724589</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>148</v>
+        <v>1555</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>46.53133680102194</v>
+        <v>63.9909333818806</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>21.34246387741439</v>
+        <v>23.65647739318278</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.059137028705434</v>
+        <v>0.2183950199595346</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.2906594861168976</v>
+        <v>11.54318631018933</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8050</v>
+        <v>8093</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>547.6493392319791</v>
+        <v>595.47704515431</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>52.2</v>
+        <v>19.95</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>44.05241971908021</v>
+        <v>54.1232303901816</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>28.57523743400916</v>
+        <v>8.621656161694233</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.4080072982898173</v>
+        <v>0.6818939541671647</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.9118139157755112</v>
+        <v>0.2638735617345867</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8049</v>
+        <v>8105</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>523.1724974149606</v>
+        <v>591.0169497811215</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>27.1</v>
+        <v>21.65</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>50.17795571554093</v>
+        <v>53.60222502810628</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>27.16001369299875</v>
+        <v>40.80834217791806</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.3572702589200145</v>
+        <v>0.5806957463653735</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.0511553367299006</v>
+        <v>-0.1979623809766324</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8064</v>
+        <v>8054</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>521.4779975722799</v>
+        <v>587.7752536229385</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>148</v>
+        <v>118.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,49 +1824,49 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>53.4917363483116</v>
+        <v>56.44474740812772</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>27.25936718831002</v>
+        <v>24.1442656770562</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.04101525642914</v>
+        <v>0.7761839384361525</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-2.37086240201322</v>
+        <v>1.270097715189874</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8476</v>
+        <v>8215</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>517.2083378142471</v>
+        <v>578.645088663881</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>24.75</v>
+        <v>29.15</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>90.44881082790404</v>
+        <v>49.09041104832122</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>63.02425696907693</v>
+        <v>23.92634766565858</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.7449097332396131</v>
+        <v>0.4006646869277015</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.4350301317883673</v>
+        <v>-0.2076470510805771</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8473</v>
+        <v>8932</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>513.3587130166557</v>
+        <v>576.3858984873704</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>48.6</v>
+        <v>108</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,49 +1930,49 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>50.54018799760441</v>
+        <v>56.69210204752653</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>25.57506613924848</v>
+        <v>20.24330497396205</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.4942138543486997</v>
+        <v>0.5385898487370345</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.7842429543992315</v>
+        <v>0.5644942539948399</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8131</v>
+        <v>8070</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>508.5179803798932</v>
+        <v>560.670902559927</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>69.3</v>
+        <v>53.4</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,49 +1983,49 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>46.72888094859509</v>
+        <v>46.76671932493435</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>13.20649091082138</v>
+        <v>22.53365188823351</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.8865415063730595</v>
+        <v>0.2913434859648606</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.7441324803875911</v>
+        <v>-0.8773341700201558</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8088</v>
+        <v>8147</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>507.1934068928559</v>
+        <v>553.4478054620835</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>60.2</v>
+        <v>148</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>46.30633554271227</v>
+        <v>46.5313368138928</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>24.08638149430238</v>
+        <v>21.34246390755758</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.4167086992933254</v>
+        <v>1.059137028705434</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.6869719513150039</v>
+        <v>0.2906594862123031</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8162</v>
+        <v>9905</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>486.9858313270825</v>
+        <v>550.7537189274993</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>77.2</v>
+        <v>21.25</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>54.93486038993835</v>
+        <v>61.41545196594335</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>40.10332382233811</v>
+        <v>19.69913792585664</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.3928621190998826</v>
+        <v>0.4241903379002227</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.5160864400427769</v>
+        <v>0.052637498522428</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8072</v>
+        <v>8050</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>484.9900412921818</v>
+        <v>547.6493392319791</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>29.2</v>
+        <v>52.2</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>50.80939564303962</v>
+        <v>44.05241961578221</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>23.91713682225708</v>
+        <v>28.57523776393141</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.2777121715453796</v>
+        <v>0.4080072982898173</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.0792589611526068</v>
+        <v>-0.9118139154320832</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8183</v>
+        <v>8481</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>465.7267858769903</v>
+        <v>536.8287522364858</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>34.05</v>
+        <v>41.7</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>58.10962152130483</v>
+        <v>54.43638331535195</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>19.31221677021287</v>
+        <v>22.58013804606061</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.8726785876990272</v>
+        <v>1.827825054423115</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.2713294803209648</v>
+        <v>-0.0444403573668023</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8499</v>
+        <v>8049</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>431.6884956190485</v>
+        <v>523.1724974149606</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>300.5</v>
+        <v>27.1</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>50.59165614979263</v>
+        <v>50.17795567580679</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>16.96916761172215</v>
+        <v>27.16001374801915</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.5168720431073091</v>
+        <v>0.3572702589200145</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.1424625297687605</v>
+        <v>-0.0511553366917418</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8104</v>
+        <v>8064</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>429.1320238521964</v>
+        <v>521.4779975722799</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>37.55</v>
+        <v>148</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,49 +2301,49 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>45.3745309030702</v>
+        <v>53.49173634290786</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>22.11725438149919</v>
+        <v>27.25936699947283</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.2374495232272931</v>
+        <v>1.04101525642914</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.5778693488634153</v>
+        <v>-2.370862401812871</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8110</v>
+        <v>9136</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>422.0743227285797</v>
+        <v>519.7262567219384</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>54.1</v>
+        <v>14</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>46.41241265921887</v>
+        <v>51.49867230049455</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>19.22786579491468</v>
+        <v>40.86227595608664</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.5537386865273047</v>
+        <v>0.0789510128904041</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.5774622119436457</v>
+        <v>-0.6782081186184568</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8155</v>
+        <v>8476</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>417.7985833472181</v>
+        <v>517.2083378142471</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>376</v>
+        <v>24.75</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>46.7781990910088</v>
+        <v>90.44881083027929</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>16.5220164000781</v>
+        <v>63.02425706801787</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.652600169086814</v>
+        <v>0.7449097332396131</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-1.371029786978364</v>
+        <v>0.4350301318360685</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8103</v>
+        <v>8473</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>413.7362470833053</v>
+        <v>513.3587130166557</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>99.40000000000001</v>
+        <v>48.6</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>49.31767449616522</v>
+        <v>50.54018793921724</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>16.80353327697779</v>
+        <v>25.57506612995538</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.158309659921438</v>
+        <v>0.4942138543486997</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.4651055598165787</v>
+        <v>-0.7842429542275218</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8097</v>
+        <v>8131</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>378.2007823967302</v>
+        <v>508.5179803798932</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>58.7</v>
+        <v>69.3</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>51.4284735146365</v>
+        <v>46.72888094626894</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>21.605102938854</v>
+        <v>13.20649085016427</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.6153494657721399</v>
+        <v>0.8865415063730595</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.2365278469392713</v>
+        <v>-0.7441324803589771</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8111</v>
+        <v>8088</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>376.7341796037434</v>
+        <v>507.193406892856</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>52.3</v>
+        <v>60.2</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>35.27115426764431</v>
+        <v>46.30633550637359</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>27.35290037877445</v>
+        <v>24.08638140356471</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.7644387771019303</v>
+        <v>0.4167086992933254</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.1926360489688767</v>
+        <v>-0.6869719511051322</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8210</v>
+        <v>8358</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>369.4448106251783</v>
+        <v>491.0081800435783</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>1295</v>
+        <v>587</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,49 +2619,49 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>46.4556794163742</v>
+        <v>50.82474262534138</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>16.15747970021336</v>
+        <v>19.43468691048406</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.5911090452512445</v>
+        <v>1.456799230742878</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-19.03305527176915</v>
+        <v>-13.61653962067126</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8086</v>
+        <v>8162</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>359.2792827862272</v>
+        <v>486.9858313270825</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>143.5</v>
+        <v>77.2</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,49 +2672,49 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>42.55913757920098</v>
+        <v>54.93486042643435</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>16.48619092801401</v>
+        <v>40.10332381996368</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.8962154069116324</v>
+        <v>0.3928621190998826</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-1.895771310021184</v>
+        <v>-0.5160864400332503</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8074</v>
+        <v>8072</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>356.2862853567541</v>
+        <v>484.990041292183</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>67.2</v>
+        <v>29.2</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>42.39584730798288</v>
+        <v>50.80939546249744</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>10.91771907089492</v>
+        <v>23.9171367980795</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.5988896540820132</v>
+        <v>0.2777121715453796</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.5281071509748285</v>
+        <v>-0.0792589610762944</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8422</v>
+        <v>9105</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>354.8212311485042</v>
+        <v>481.3060744705177</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>27</v>
+        <v>9.41</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,49 +2778,49 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>41.56850278859179</v>
+        <v>53.23973832853491</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>13.59235475750666</v>
+        <v>35.90666321658704</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.146786635273807</v>
+        <v>0.7628074361294614</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.1665211915288389</v>
+        <v>-0.1830771864501632</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8341</v>
+        <v>8454</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>352.6269236059839</v>
+        <v>476.2109262359709</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>75.8</v>
+        <v>276</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>37.06386346771427</v>
+        <v>43.86786544985819</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>23.18325532620882</v>
+        <v>43.01097389740996</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.5027824880802828</v>
+        <v>0.7970825406401965</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.6100194880274257</v>
+        <v>-12.97437362506811</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8076</v>
+        <v>8411</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>350.5627339967783</v>
+        <v>474.5063962075309</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>24.85</v>
+        <v>12.15</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>46.44865361847464</v>
+        <v>51.98818613148801</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>15.49411229519926</v>
+        <v>38.71690371246863</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.2406520255416949</v>
+        <v>0.4487434707242733</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.2778904313115847</v>
+        <v>0.0017322738582518</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8080</v>
+        <v>8240</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>339.523810379097</v>
+        <v>474.4341730645358</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>27.75</v>
+        <v>51.3</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>46.21683781788526</v>
+        <v>36.02493949182026</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>47.06382694423503</v>
+        <v>15.63255684455545</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.9042119261543964</v>
+        <v>0.4337893548671089</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.0242976062140366</v>
+        <v>-0.3734682899579824</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8084</v>
+        <v>8183</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>330.1960998704898</v>
+        <v>465.7267858769903</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>49.05</v>
+        <v>34.05</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>54.83645756675395</v>
+        <v>58.10962141481892</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>18.40280980961612</v>
+        <v>19.31221688181925</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.6454158231159436</v>
+        <v>0.8726785876990272</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.0238060670619185</v>
+        <v>0.2713294806643982</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>9930</v>
+        <v>8482</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>307.4082506657213</v>
+        <v>463.6055369695774</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>65.90000000000001</v>
+        <v>48.1</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>28.87330563632138</v>
+        <v>51.59947440325407</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>25.6605003448418</v>
+        <v>7.959247187995412</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.8764236365519245</v>
+        <v>0.3065325492155037</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.3875858699048083</v>
+        <v>1.30805103118491</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8114</v>
+        <v>8277</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>305.4398257184493</v>
+        <v>442.4974605325613</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>182.5</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>32.77432210427223</v>
+        <v>48.10543736631485</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>22.29598801594764</v>
+        <v>26.03786195606276</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.3869294912426474</v>
+        <v>0.3740522758545515</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-3.867924671834397</v>
+        <v>-0.1966191164242442</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8067</v>
+        <v>8383</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>295.6999072640733</v>
+        <v>434.1890815200801</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>12.9</v>
+        <v>61.8</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>50.11433908531635</v>
+        <v>52.73917928613634</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>7.577162018028474</v>
+        <v>20.58707436239298</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.3688189086095483</v>
+        <v>1.434339755889776</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.044128512717134</v>
+        <v>0.2437560577084276</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8171</v>
+        <v>8499</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>292.5976652087361</v>
+        <v>431.6884956190485</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>21.15</v>
+        <v>300.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>42.7074775923293</v>
+        <v>50.59165615556879</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>20.07132282105488</v>
+        <v>16.9691675421222</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4048759132037087</v>
+        <v>0.5168720431073091</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.0529627007724519</v>
+        <v>0.1424625302457665</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8068</v>
+        <v>8104</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>288.5260106108825</v>
+        <v>429.1320238521964</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>18.75</v>
+        <v>37.55</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>42.35607144299471</v>
+        <v>45.37453069185192</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>19.47736713088327</v>
+        <v>22.11725431011048</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.3440038851893618</v>
+        <v>0.2374495232272931</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0518925957089374</v>
+        <v>-0.5778693483768887</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8102</v>
+        <v>9906</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>欣巴巴</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>286.1492569045874</v>
+        <v>422.1287317829185</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>67.8</v>
+        <v>41.35</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>44.27328040351166</v>
+        <v>50.73510212469718</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>13.50432631142409</v>
+        <v>37.07232724041334</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.4406289101355378</v>
+        <v>0.1854073972313417</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.8022831391380386</v>
+        <v>-0.5338609327152857</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8271</v>
+        <v>8110</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>285.0453591685217</v>
+        <v>422.0743227285797</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>180</v>
+        <v>54.1</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,49 +3361,49 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>32.21442601997651</v>
+        <v>46.41241265718656</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>17.88048329588452</v>
+        <v>19.22786578713888</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.9106054154240646</v>
+        <v>0.5537386865273047</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-2.780895441445998</v>
+        <v>-0.5774622119054831</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8087</v>
+        <v>8488</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>231.4311860948568</v>
+        <v>418.8077371798725</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>32.35</v>
+        <v>10</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>41.80470273629104</v>
+        <v>51.4628555021535</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>13.58458957986164</v>
+        <v>15.63977539511212</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.4018747915435433</v>
+        <v>0.1082834493384281</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.2005365736215294</v>
+        <v>-0.4229696393466111</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8213</v>
+        <v>8155</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>216.0334298860771</v>
+        <v>417.7985833472181</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>35.6</v>
+        <v>376</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>43.32844532357146</v>
+        <v>46.7781990910088</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>11.67383571489494</v>
+        <v>16.52201637880176</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.8620109332547338</v>
+        <v>0.652600169086814</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.0550180585836583</v>
+        <v>-1.371029786215219</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8048</v>
+        <v>8103</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>214.5134107222776</v>
+        <v>413.7362470833053</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>61.9</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>46.03532461612307</v>
+        <v>49.31767445431856</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>15.5318009790341</v>
+        <v>16.80353331021201</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.5403767124555975</v>
+        <v>1.158309659921438</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.4204629059035292</v>
+        <v>0.4651055599473772</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8089</v>
+        <v>8234</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>208.2175602373984</v>
+        <v>406.5241126921201</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>19.9</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>44.2806512085058</v>
+        <v>51.71111314705256</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>30.16414577037403</v>
+        <v>20.47082283021557</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.2722889595914037</v>
+        <v>0.750864634022008</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.1008448812710504</v>
+        <v>0.4730051130937397</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>9955</v>
+        <v>8462</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>195.0862186297984</v>
+        <v>400.7608321329818</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>26.3</v>
+        <v>143</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>38.49520989780745</v>
+        <v>54.57268576512438</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>23.91787006318023</v>
+        <v>18.83673037913974</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.5229525061375463</v>
+        <v>0.814344974354285</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.002895489956487</v>
+        <v>0.2691022605433908</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, foreign_buy_3d, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8101</v>
+        <v>8097</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>184.0778088356639</v>
+        <v>378.2007823967302</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>12.75</v>
+        <v>58.7</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>39.07654195581286</v>
+        <v>51.42847337306298</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>14.0304945137058</v>
+        <v>21.60510298101191</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.3142879888683901</v>
+        <v>0.6153494657721399</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.2943294678616175</v>
+        <v>-0.2365278467293968</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8092</v>
+        <v>8111</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>177.7200858232768</v>
+        <v>376.7341796037434</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>13.3</v>
+        <v>52.3</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>26.55092099782304</v>
+        <v>35.27115437815824</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>20.4428480961836</v>
+        <v>27.35290038211896</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.5720196620971356</v>
+        <v>0.7644387771019303</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.1324762751606956</v>
+        <v>-0.1926360489116283</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8059</v>
+        <v>8210</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>161.9181228722707</v>
+        <v>369.4448106251783</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>16.3</v>
+        <v>1295</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,49 +3785,49 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>32.29586495416856</v>
+        <v>46.45567942101066</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>21.52830595468004</v>
+        <v>16.15747968698585</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.873085877094844</v>
+        <v>0.5911090452512445</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M63" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.09861845521334579</v>
+        <v>-19.03305526957501</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8201</v>
+        <v>8291</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>150.6685888274262</v>
+        <v>367.9375850926198</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>12.9</v>
+        <v>42</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>44.95474553310149</v>
+        <v>39.65544440689831</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>17.87571441789742</v>
+        <v>26.31602397957366</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.37150009046731</v>
+        <v>0.2925233325768363</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.0707924052409805</v>
+        <v>-1.690745921748813</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8249</v>
+        <v>8390</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>148.4472372604689</v>
+        <v>367.6625078066564</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>48.05</v>
+        <v>104</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>40.74369144864785</v>
+        <v>39.59243143578195</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>17.61163914908903</v>
+        <v>21.73979288788022</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.005440631198076</v>
+        <v>0.7100261499512504</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,62 +3909,2765 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.5563345873294627</v>
+        <v>-1.768355503202442</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
+        <v>9907</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>統一實</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>366.6394518061432</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>40.09254840498434</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>29.62683836988729</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>1.37836515577247</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>-0.08299931677255851</v>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>8086</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>宏捷科</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>359.2792827862272</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>42.55913760483375</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>16.48619088970386</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>0.8962154069116324</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>-1.895771309811332</v>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>8074</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>鉅橡</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>356.2862853567541</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>42.39584730689735</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>10.91771894823591</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>0.5988896540820132</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>-0.5281071509366724</v>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>8422</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>可寧衛*</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>354.8212311485042</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>41.56850344138696</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>13.59235472636221</v>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>1.146786635273807</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N69" s="2" t="n">
+        <v>-0.1665211913653444</v>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>8299</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>群聯</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>353.701411130111</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>2270</v>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>45.29508397129219</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>11.69657380136634</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>0.7693762849978464</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>-20.01819434271374</v>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>8341</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>日友</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>352.6269236059839</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>37.06386339799558</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>23.18325535369896</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>0.5027824880802828</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>-0.6100194878366151</v>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>8076</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>伍豐</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>350.5627339967783</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>46.44865341944029</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>15.4941123546378</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>0.2406520255416949</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>-0.2778904311207929</v>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>8080</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>永利聯合</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>339.523810379097</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>46.21683796260826</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>47.06382705356075</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>0.9042119261543964</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N73" s="2" t="n">
+        <v>-0.0242976062140366</v>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>8084</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>巨虹</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>330.1960998704898</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>54.83645756675395</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>18.40280978849965</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>0.6454158231159436</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>-0.0238060669951334</v>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>9908</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>大台北</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>322.1606534798674</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>60.18129310213274</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>19.55415769437089</v>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>1.471660771322807</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N75" s="2" t="n">
+        <v>0.0238154383896945</v>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>8455</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>大拓-KY</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>307.4197555913954</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>40.6312240267945</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>19.39547004359398</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>0.1662538881874465</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v>-0.59518704408274</v>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>9930</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>中聯資源</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>307.4082506657213</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>28.87330544885669</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>25.66050039582277</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>0.8764236365519245</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>-0.3875858696567836</v>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>8114</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>振樺電</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>305.4398257184493</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>32.77432201998711</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>22.29598816892197</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>0.3869294912426474</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>-3.867924669735643</v>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>9911</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>櫻花</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>296.4993198696092</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>52.07819744525425</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>10.82498301213491</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>1.459782400362714</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N79" s="2" t="n">
+        <v>-0.0085029616469075</v>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>8067</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>志旭</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>295.6999072640733</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>50.11433907760053</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>7.577161995559835</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>0.3688189086095483</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>-0.0441285127743732</v>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>8171</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>天宇</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>292.5976652087361</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>42.70747758135462</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>20.07132277684431</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>0.4048759132037087</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>-0.0529627007915327</v>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>8068</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>全達</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>288.5260106108825</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>42.35607139444567</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>19.47736712850808</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>0.3440038851893618</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>0.0518925957661747</v>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>8102</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>傑霖科技</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>286.1492569045874</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>44.27328040661206</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>13.50432631142409</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>0.4406289101355378</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>-0.8022831391571239</v>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>8271</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>宇瞻</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>285.0453591685217</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>32.21442599923077</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>17.88048315714562</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>0.9106054154240646</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>-2.780895440988077</v>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>8443</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>阿瘦</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>284.7868326323725</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>47.12239891554694</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>51.80134986259949</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>0.2555722177362505</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>0.0149827923951232</v>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>8472</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>夠麻吉</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>283.822956691139</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>46.93939672339854</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>18.32809497948172</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0.197524473733843</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>-1.140848068527349</v>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>8367</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>建新國際</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>279.5139686911643</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>41.77190786654873</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>22.79609966871295</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>0.8251296696610485</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>0.0560434714864412</v>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>9904</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>寶成</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>274.5971775211019</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>32.99831460604894</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>16.33081877693596</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>2.35971775211019</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>-0.118936157348579</v>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>8478</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>東哥遊艇</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>268.2907766995863</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>153.5</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>48.7905831427892</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>12.01856322500724</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>0.502652387698194</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>0.2019654136849813</v>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>8374</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>羅昇</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>265.8523865225215</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>41.55586874215914</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>14.35268068719545</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>0.6022807487096133</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>-0.9669882559203508</v>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>美德醫療-DR</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>254.8361257911609</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>42.16691368851154</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>20.49711044836921</v>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>0.2640561295634553</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N91" s="2" t="n">
+        <v>-0.0626165704904349</v>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>8087</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>華鎂鑫</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>231.4311860948568</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>41.80470264968097</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>13.5845896541026</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>0.4018747915435433</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>-0.2005365736215294</v>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>8431</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>匯鑽科</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>230.751313230512</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>44.93599551676917</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>12.07124118243501</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>0.3459587568398591</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>0.1992635728383285</v>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>8477</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>創業家</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>229.0049547177859</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>42.87570439984008</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>21.36504212999533</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>0.6681435465255885</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N94" s="2" t="n">
+        <v>-0.254787892340629</v>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>8404</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>百和興業-KY</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>222.5408378302395</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>45.97875915981425</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>11.9583251274052</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>1.024021167132692</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>-0.0233961464613944</v>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>8213</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>志超</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>216.0334298860771</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>43.32844533551086</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>11.67383571923784</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>0.8620109332547338</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v>-0.0550180585168708</v>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>8048</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>德勝</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>214.5134107222776</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>46.0353246063863</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>15.53180092855376</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>0.5403767124555975</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>-0.4204629058653703</v>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>8089</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>康全電訊</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>208.2175602373988</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>44.28065037309177</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>30.16414576742774</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>0.2722889595914037</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>-0.1008448807559033</v>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>9910</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>豐泰</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>196.9968519433162</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>40.63937846610672</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>19.34410626269895</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>0.2472956360008465</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>-1.269333625321558</v>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>9955</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>佳龍</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>195.0862186297978</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>38.49520984577969</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>23.91787009619736</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>0.5229525061375463</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>-0.0028954899755657</v>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>8101</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>華冠</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>184.0778088356638</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>39.07654192998036</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>14.03049455669586</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>0.3142879888683901</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>-0.2943294678234592</v>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>8410</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>森田</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>183.6313849634408</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>43.85502324610788</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>19.3977599139349</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>0.5451839034536586</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>0.0670833143364901</v>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>9110</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>越南控-DR</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>181.1167582662896</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>52.12461831282545</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>15.43583474597558</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>0.1463833660588873</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>-0.0065426859951327</v>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>8092</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>建暐</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>177.7200858232768</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>26.55092095287486</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>20.44284808969426</v>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>0.5720196620971356</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>-0.1324762751416168</v>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>8940</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>新天地</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>169.4086314823329</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>48.09479033998809</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>16.54288929848664</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>0.2251269535250332</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>0.0209267184889503</v>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>8059</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>凱碩</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>161.9181228722707</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>32.2958645341172</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>21.52830609089053</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>0.873085877094844</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>-0.0986184548222185</v>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>8487</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>愛爾達-創</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>159.0446221118462</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>43.82816622727262</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>11.61294072838044</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>0.7077650984299753</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>-0.2399362156167493</v>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>9802</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>鈺齊-KY</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>150.8256814665397</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>35.89292760011578</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>17.04878381662212</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>0.6804146410817912</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>-0.566150670059215</v>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>無敵</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>150.6685888274262</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>44.95474553310149</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>17.87571447892875</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>0.37150009046731</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>-0.07079240525051921</v>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>8249</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>菱光</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>148.4472372604689</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>48.05</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>40.74369134988455</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>17.61163907442107</v>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>1.005440631198076</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>-0.5563345871577426</v>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>8423</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>保綠-KY</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>142.0183078952147</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>45.31003945272199</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>9.889015299974565</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>0.5931721915026467</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>-0.0044884400860302</v>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>8440</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>綠電</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>140.2115243129193</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>21.35</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>41.34332752200683</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>10.8876012951341</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>0.4784633373108403</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>-0.1079025190186507</v>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>8429</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>金麗-KY</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>118.9479484942571</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>37.18289572425252</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>18.37954958243621</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>0.4499944227102979</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>-0.045366246646743</v>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>8463</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>潤泰材</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>93.2377396104538</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>43.26795407002992</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>14.71615505607398</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0.7787360078047039</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>-0.0384667282773862</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>8467</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>波力-KY</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>87.80694372460962</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>46.63679592671673</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>11.1465622460529</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>1.372860787478523</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>0.6532061923052583</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
         <v>8085</v>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>福華</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D66" s="2" t="n">
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
         <v>74.15288557183288</v>
       </c>
-      <c r="E66" s="2" t="n">
+      <c r="E116" s="2" t="n">
         <v>11.8</v>
       </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H66" s="2" t="n">
-        <v>42.4280193213454</v>
-      </c>
-      <c r="I66" s="2" t="n">
-        <v>18.0145741041381</v>
-      </c>
-      <c r="J66" s="2" t="n">
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>42.42801921273909</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>18.01457413188176</v>
+      </c>
+      <c r="J116" s="2" t="n">
         <v>0.2565887218093056</v>
       </c>
-      <c r="K66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N66" s="2" t="n">
-        <v>-0.1221104786347467</v>
-      </c>
-      <c r="O66" s="2" t="inlineStr">
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>-0.1221104785011899</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>9902</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>台火</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>74.01169001384952</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>43.32230214608621</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>14.42937377025641</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.4277549338133249</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>0.0056019035104252</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
